--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484160_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484160_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.7781</v>
+        <v>11.4194</v>
       </c>
       <c r="E2" t="n">
-        <v>10.8673</v>
+        <v>11.4625</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9107</v>
+        <v>-0.0431</v>
       </c>
       <c r="G2" t="n">
         <v>4.1988</v>
@@ -610,13 +610,13 @@
         <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1033</v>
+        <v>-0.462</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1902</v>
+        <v>-0.595</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0869</v>
+        <v>0.133</v>
       </c>
       <c r="V2" t="n">
         <v>5.5004</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1272</v>
+        <v>1.5809</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6534</v>
+        <v>2.574</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5262</v>
+        <v>-0.9931</v>
       </c>
       <c r="G3" t="n">
         <v>2.7547</v>
@@ -688,13 +688,13 @@
         <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2146</v>
+        <v>-0.7609</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1359</v>
+        <v>-0.2153</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0787</v>
+        <v>-0.5457</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2065</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7062</v>
+        <v>0.9406</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2877</v>
+        <v>0.1431</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9939</v>
+        <v>0.7975</v>
       </c>
       <c r="G4" t="n">
         <v>0.4112</v>
@@ -766,13 +766,13 @@
         <v>0.7935</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2318</v>
+        <v>0.4662</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1303</v>
+        <v>0.3005</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3621</v>
+        <v>0.1657</v>
       </c>
       <c r="V4" t="n">
         <v>-0.532</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4482</v>
+        <v>0.8753</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1559</v>
+        <v>2.2182</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7077</v>
+        <v>-1.343</v>
       </c>
       <c r="G5" t="n">
         <v>2.8572</v>
@@ -844,13 +844,13 @@
         <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7544</v>
+        <v>-0.3273</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3797</v>
+        <v>-0.3173</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3747</v>
+        <v>-0.01</v>
       </c>
       <c r="V5" t="n">
         <v>-0.266</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7488</v>
+        <v>-1.7691</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8972</v>
+        <v>0.8769</v>
       </c>
       <c r="F6" t="n">
         <v>-2.646</v>
@@ -922,10 +922,10 @@
         <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4932</v>
+        <v>-0.5271</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2301</v>
+        <v>0.2098</v>
       </c>
       <c r="U6" t="n">
         <v>-0.7369</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.9315</v>
+        <v>-2.6589</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5994</v>
+        <v>-1.2707</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3321</v>
+        <v>-1.3882</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4317</v>
@@ -1000,13 +1000,13 @@
         <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5079</v>
+        <v>-0.2352</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3741</v>
+        <v>-0.0453</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1338</v>
+        <v>-0.1899</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0646</v>
+        <v>-2.8161</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.575</v>
+        <v>-1.4107</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4896</v>
+        <v>-1.4054</v>
       </c>
       <c r="G8" t="n">
         <v>-2.7406</v>
@@ -1078,13 +1078,13 @@
         <v>0.5952</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1852</v>
+        <v>-0.9367</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5611</v>
+        <v>-0.3967</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6241</v>
+        <v>-0.5399</v>
       </c>
       <c r="V8" t="n">
         <v>0.266</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6995</v>
+        <v>-3.5405</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1692</v>
+        <v>0.3562</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.8687</v>
+        <v>-3.8967</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5504</v>
@@ -1156,13 +1156,13 @@
         <v>2.1822</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6649</v>
+        <v>-0.5059</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3229</v>
+        <v>-0.1359</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3419</v>
+        <v>-0.37</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4842</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.8153</v>
+        <v>-5.2964</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6198</v>
+        <v>-2.3534</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1955</v>
+        <v>-2.943</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9687</v>
@@ -1234,13 +1234,13 @@
         <v>1.5871</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.5013</v>
+        <v>-1.9824</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3092</v>
+        <v>-1.0428</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1921</v>
+        <v>-0.9396</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9405</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.199999999999998</v>
+        <v>-1.264800000000003</v>
       </c>
       <c r="E11" t="n">
-        <v>11.6611</v>
+        <v>12.5961</v>
       </c>
       <c r="F11" t="n">
-        <v>-13.8612</v>
+        <v>-13.861</v>
       </c>
       <c r="G11" t="n">
         <v>1.9513</v>
@@ -1312,13 +1312,13 @@
         <v>11.9031</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.2066</v>
+        <v>-5.2713</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.1733</v>
+        <v>-2.238</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.0332</v>
+        <v>-3.0333</v>
       </c>
       <c r="V11" t="n">
         <v>0.07119999999999982</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.5712</v>
+        <v>6.2753</v>
       </c>
       <c r="E12" t="n">
-        <v>6.6951</v>
+        <v>6.287</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1239</v>
+        <v>-0.0117</v>
       </c>
       <c r="G12" t="n">
         <v>4.8366</v>
@@ -1390,13 +1390,13 @@
         <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>0.806</v>
+        <v>0.5101</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.4876</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0897</v>
+        <v>0.0226</v>
       </c>
       <c r="V12" t="n">
         <v>0.3334</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1754</v>
+        <v>4.04</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7815</v>
+        <v>4.3937</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6062</v>
+        <v>-0.3537</v>
       </c>
       <c r="G13" t="n">
         <v>3.2173</v>
@@ -1468,13 +1468,13 @@
         <v>1.3887</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1683</v>
+        <v>1.033</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2777</v>
+        <v>0.3345</v>
       </c>
       <c r="U13" t="n">
-        <v>0.446</v>
+        <v>0.6985</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6071</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4426</v>
+        <v>1.5089</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9444</v>
+        <v>1.8424</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5018</v>
+        <v>-0.3335</v>
       </c>
       <c r="G14" t="n">
         <v>0.0449</v>
@@ -1546,13 +1546,13 @@
         <v>0.7935</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9908</v>
+        <v>1.0571</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6519</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3389</v>
+        <v>0.5072</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3866</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.075</v>
+        <v>-0.2432</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5617</v>
+        <v>0.7715</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4868</v>
+        <v>-1.0148</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.0129</v>
+        <v>0.7985</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5359</v>
+        <v>0.5847</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.477</v>
+        <v>0.2138</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1193</v>
+        <v>3.8217</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4818</v>
+        <v>2.0469</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6375</v>
+        <v>1.7748</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.8937</v>
+        <v>-3.0232</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0541</v>
+        <v>-1.4622</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8395</v>
+        <v>-1.561</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1984</v>
+        <v>-2.579</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9838</v>
+        <v>-3.9677</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6568</v>
+        <v>0.384</v>
       </c>
       <c r="T15" t="n">
-        <v>0.72</v>
+        <v>-0.289</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9368</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>2.6295</v>
+        <v>1.1533</v>
       </c>
       <c r="W15" t="n">
-        <v>2.9449</v>
+        <v>1.2065</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3154</v>
+        <v>-0.0532</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3785</v>
+        <v>-0.3794</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1593</v>
+        <v>0.2242</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.6036</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7985</v>
+        <v>-0.1815</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5847</v>
+        <v>-0.1815</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2138</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8217</v>
+        <v>0.0202</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0469</v>
+        <v>0.0202</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7748</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0232</v>
+        <v>-0.2016</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4622</v>
+        <v>-0.2016</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.561</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.579</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2487</v>
+        <v>0.068</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9011</v>
+        <v>0.2041</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1499</v>
+        <v>-0.136</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1533</v>
+        <v>-0.266</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.0532</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5835</v>
+        <v>-0.5856</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0202</v>
+        <v>0.1536</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6036</v>
+        <v>-0.7393</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1815</v>
+        <v>-4.0129</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1815</v>
+        <v>-1.5359</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-2.477</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0202</v>
+        <v>-1.1193</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0202</v>
+        <v>-0.4818</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.6375</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2016</v>
+        <v>-2.8937</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2016</v>
+        <v>-1.0541</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-1.8395</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.7855</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.136</v>
+        <v>0.9962</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.3119</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.136</v>
+        <v>0.6843</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.266</v>
+        <v>2.6295</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.9449</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.266</v>
+        <v>-0.3154</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. DE LEON</t>
+          <t>A. BENNASAR ROJO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7905</v>
+        <v>-0.9912</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7114</v>
+        <v>0.2556</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5019</v>
+        <v>-1.2467</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.3213</v>
+        <v>-0.155</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5064</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8149</v>
+        <v>-0.2254</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4835</v>
+        <v>0.0402</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6441</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1606</v>
+        <v>0.0402</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.8378</v>
+        <v>-0.1951</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8623</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.9756</v>
+        <v>-0.2656</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3968</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3893</v>
+        <v>0.6362</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3888</v>
+        <v>0.2154</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0005</v>
+        <v>0.4208</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7447</v>
+        <v>-1.4724</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.0532</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BENNASAR ROJO</t>
+          <t>D. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-1.0637</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0515</v>
+        <v>1.6842</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9381</v>
+        <v>-2.7479</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.155</v>
+        <v>-0.4785</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07049999999999999</v>
+        <v>-0.6301</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2254</v>
+        <v>0.1516</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0402</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.6452</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0402</v>
+        <v>0.0026</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1951</v>
+        <v>-1.1262</v>
       </c>
       <c r="N19" t="n">
-        <v>0.07049999999999999</v>
+        <v>-1.2753</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2656</v>
+        <v>0.149</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1936,28 +1936,28 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7408</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0113</v>
+        <v>-0.17</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7294</v>
+        <v>-0.4152</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. POU BLINNIKOV</t>
+          <t>R. DE LEON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2398</v>
+        <v>-1.6144</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4801</v>
+        <v>-0.3089</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7199</v>
+        <v>-1.3055</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4785</v>
+        <v>-3.3213</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6301</v>
+        <v>-1.5064</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1516</v>
+        <v>-1.8149</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6477000000000001</v>
+        <v>-0.4835</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6452</v>
+        <v>-0.6441</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0026</v>
+        <v>0.1606</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1262</v>
+        <v>-2.8378</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2753</v>
+        <v>-0.8623</v>
       </c>
       <c r="O20" t="n">
-        <v>0.149</v>
+        <v>-1.9756</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.3968</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7612</v>
+        <v>0.5654</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3741</v>
+        <v>0.3685</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3872</v>
+        <v>0.1969</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.7447</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2065</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2065</v>
+        <v>-0.0532</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4376</v>
+        <v>-2.3713</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2719</v>
+        <v>0.1698</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7095</v>
+        <v>-2.5412</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1774</v>
@@ -2092,13 +2092,13 @@
         <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.8077</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4649</v>
+        <v>0.3628</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2766</v>
+        <v>0.4449</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7476</v>
+        <v>-2.3752</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8161</v>
+        <v>-1.612</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9315</v>
+        <v>-0.7632</v>
       </c>
       <c r="G22" t="n">
         <v>0.478</v>
@@ -2170,13 +2170,13 @@
         <v>0.7935</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3616</v>
+        <v>0.734</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4535</v>
+        <v>0.6576</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0919</v>
+        <v>0.0764</v>
       </c>
       <c r="V22" t="n">
         <v>-1.405</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.2001</v>
+        <v>2.2002</v>
       </c>
       <c r="E23" t="n">
-        <v>13.861</v>
+        <v>13.8611</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.661</v>
+        <v>-11.6611</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.951300000000001</v>
+        <v>-1.9513</v>
       </c>
       <c r="H23" t="n">
         <v>5.368399999999999</v>
@@ -2233,7 +2233,7 @@
         <v>-15.3868</v>
       </c>
       <c r="N23" t="n">
-        <v>-6.2542</v>
+        <v>-6.254200000000001</v>
       </c>
       <c r="O23" t="n">
         <v>-9.132800000000001</v>
@@ -2251,7 +2251,7 @@
         <v>6.2065</v>
       </c>
       <c r="T23" t="n">
-        <v>3.0332</v>
+        <v>3.0333</v>
       </c>
       <c r="U23" t="n">
         <v>3.1733</v>
@@ -2260,7 +2260,7 @@
         <v>-0.07139999999999991</v>
       </c>
       <c r="W23" t="n">
-        <v>9.295500000000001</v>
+        <v>9.295499999999999</v>
       </c>
       <c r="X23" t="n">
         <v>-9.3667</v>
